--- a/en/downloads/data-excel/6.4.2.1.xlsx
+++ b/en/downloads/data-excel/6.4.2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274B93C5-CA2A-4505-BD99-6ACD065174B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,10 +20,19 @@
     <definedName name="Button_1">"Pokreal_CHC_List"</definedName>
     <definedName name="Button_2">"Pokreal_CHC_List"</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -190,7 +200,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
@@ -413,7 +423,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -430,30 +440,18 @@
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -475,7 +473,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -487,13 +485,29 @@
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -504,28 +518,28 @@
     </xf>
   </cellXfs>
   <cellStyles count="22">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="8"/>
-    <cellStyle name="Обычный 11" xfId="21"/>
-    <cellStyle name="Обычный 2" xfId="6"/>
-    <cellStyle name="Обычный 2 2" xfId="9"/>
-    <cellStyle name="Обычный 2 3" xfId="10"/>
-    <cellStyle name="Обычный 3" xfId="11"/>
-    <cellStyle name="Обычный 3 2" xfId="12"/>
-    <cellStyle name="Обычный 4" xfId="4"/>
-    <cellStyle name="Обычный 5" xfId="5"/>
-    <cellStyle name="Обычный 6" xfId="7"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
-    <cellStyle name="Обычный 8" xfId="13"/>
-    <cellStyle name="Обычный 9" xfId="14"/>
-    <cellStyle name="Пояснение 2" xfId="15"/>
-    <cellStyle name="Процентный 2" xfId="16"/>
-    <cellStyle name="Процентный 3" xfId="17"/>
-    <cellStyle name="Стиль 1" xfId="18"/>
-    <cellStyle name="Финансовый 2" xfId="19"/>
-    <cellStyle name="Финансовый 3" xfId="20"/>
+    <cellStyle name="Обычный 10" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 11" xfId="21" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="10" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 3" xfId="11" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 4" xfId="4" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 5" xfId="5" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 6" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 8" xfId="13" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 9" xfId="14" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Пояснение 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Процентный 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Процентный 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Стиль 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Финансовый 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Финансовый 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -802,41 +816,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="3" width="34.7109375" style="19" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="3" width="34.7109375" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27" customHeight="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:14" ht="27" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="13.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:14" ht="13.5" customHeight="1" thickBot="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
+      <c r="N3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" ht="14.25" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>49</v>
       </c>
@@ -864,20 +879,23 @@
       <c r="I4" s="4">
         <v>2019</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="19">
         <v>2020</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="19">
         <v>2021</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="19">
         <v>2022</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="19">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="14.25" customHeight="1">
+      <c r="N4" s="26">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -905,27 +923,30 @@
       <c r="I5" s="5">
         <v>8068.7</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="20">
         <v>8017.9</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="20">
         <v>7999.5</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="20">
         <v>8741.9</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="20">
         <v>8872.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="N5" s="27">
+        <v>9326.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="6"/>
@@ -934,12 +955,13 @@
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-    </row>
-    <row r="7" spans="1:13" ht="14.25" customHeight="1">
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="28"/>
+    </row>
+    <row r="7" spans="1:14" ht="14.25" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
@@ -967,22 +989,25 @@
       <c r="I7" s="6">
         <v>7813.9</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="21">
         <f>J5-J8</f>
         <v>7768.0999999999995</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="21">
         <f>K5-K8</f>
         <v>7746.6</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="21">
         <v>8483.5</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="21">
         <v>8601.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="14.25" customHeight="1">
+      <c r="N7" s="28">
+        <v>9027</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="14.25" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -1010,48 +1035,52 @@
       <c r="I8" s="6">
         <v>254.8</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="21">
         <v>249.8</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="21">
         <v>252.9</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="21">
         <v>258.39999999999998</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="21">
         <v>271</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="N8" s="28">
+        <v>299.39999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A9" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-    </row>
-    <row r="10" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="29"/>
+    </row>
+    <row r="10" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A10" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="6">
@@ -1060,39 +1089,42 @@
       <c r="E10" s="6">
         <v>643.1</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>645.20000000000005</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>632.79999999999995</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <v>647.70000000000005</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <v>663.1</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="23">
         <v>757.6</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="23">
         <v>690.4</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="23">
         <v>683.8</v>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="23">
         <v>723.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="N10" s="30">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="6">
@@ -1101,39 +1133,42 @@
       <c r="E11" s="6">
         <v>985.7</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>948.9</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <v>936.2</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <v>926.6</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <v>1012.6</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <v>984.4</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="23">
         <v>968.2</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="23">
         <v>1101.8</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="23">
         <v>1205.5999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="N11" s="30">
+        <v>1288.5999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="6">
@@ -1142,275 +1177,296 @@
       <c r="E12" s="6">
         <v>578.9</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>524.6</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <v>623.70000000000005</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <v>621.1</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <v>635</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="23">
         <v>646.20000000000005</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="23">
         <v>655</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="23">
         <v>714.9</v>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="23">
         <v>779.6</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="N12" s="30">
+        <v>860.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A13" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="6">
         <v>607.70000000000005</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="6">
         <v>620.5</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="10">
         <v>607.70000000000005</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="10">
         <v>614.79999999999995</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="10">
         <v>642.29999999999995</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="10">
         <v>658.5</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="23">
         <v>667.6</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="23">
         <v>691.2</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="23">
         <v>757.9</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="23">
         <v>829.3</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="N13" s="30">
+        <v>901.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="6">
         <v>1133</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="6">
         <v>1190.0999999999999</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="10">
         <v>1125.2</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="10">
         <v>1183.5</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="10">
         <v>1144.2</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="10">
         <v>1180.8</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="23">
         <v>1147</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="23">
         <v>1248.5</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="23">
         <v>1327.6</v>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="23">
         <v>1314.9</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="N14" s="30">
+        <v>1333.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A15" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="6">
         <v>882.9</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="6">
         <v>1011.8</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="10">
         <v>944</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="10">
         <v>991.6</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="10">
         <v>963.3</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="10">
         <v>1021.3</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="23">
         <v>961.1</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="23">
         <v>959.1</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="23">
         <v>1023.7</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="23">
         <v>1034.5999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="N15" s="30">
+        <v>1172.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="6">
         <v>2833.6</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="6">
         <v>2368.1999999999998</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="10">
         <v>2367.9</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="10">
         <v>2500.5</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="10">
         <v>2634</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="10">
         <v>2707</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="23">
         <v>2664.5</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="23">
         <v>2596.6</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="23">
         <v>2929.3</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="23">
         <v>2762.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="N16" s="30">
+        <v>2745.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A17" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="6">
         <v>118.8</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="6">
         <v>113.7</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="10">
         <v>113.2</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="10">
         <v>117.7</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="10">
         <v>121.8</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="10">
         <v>133.5</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="23">
         <v>132.5</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="23">
         <v>133.6</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="23">
         <v>148.9</v>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="23">
         <v>166</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A18" s="15" t="s">
+      <c r="N17" s="30">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="12">
         <v>57.1</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="12">
         <v>57.1</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="13">
         <v>57</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="13">
         <v>57</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="13">
         <v>57</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="13">
         <v>57</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="24">
         <v>57</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="24">
         <v>57</v>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="24">
         <v>54</v>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="24">
         <v>57</v>
+      </c>
+      <c r="N18" s="31">
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>
